--- a/Auswertung/Portfolio_Profi_Analyse_B - Klever.xlsx
+++ b/Auswertung/Portfolio_Profi_Analyse_B - Klever.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Portfolio_Excel\Auswertung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787D4092-00F6-4A19-95EC-82A2A67D86A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695AAC8A-1675-452D-88B4-4EC548D686C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daten" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="224" r:id="rId9"/>
+    <pivotCache cacheId="234" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1105,7 +1105,85 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Währung" xfId="1" builtinId="4"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="46">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -7555,7 +7633,7 @@
                 <c:formatCode>_("€"* #,##0.00_);_("€"* \(#,##0.00\);_("€"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>434.54339622000009</c:v>
+                  <c:v>434.49451110000012</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8099,7 +8177,7 @@
                 <c:formatCode>_("€"* #,##0.00_);_("€"* \(#,##0.00\);_("€"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>405.00038460000002</c:v>
+                  <c:v>404.9804206500001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8156,7 +8234,7 @@
                 <c:formatCode>_("€"* #,##0.00_);_("€"* \(#,##0.00\);_("€"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>434.54339622000009</c:v>
+                  <c:v>434.49451110000012</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8921,7 +8999,7 @@
                 <c:formatCode>_("€"* #,##0.00_);_("€"* \(#,##0.00\);_("€"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>434.54339622000009</c:v>
+                  <c:v>434.49451110000012</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11204,7 +11282,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t> 405,00 € </a:t>
+            <a:t> 404,98 € </a:t>
           </a:fld>
           <a:endParaRPr lang="de-DE" sz="2800" b="1">
             <a:ln>
@@ -11294,7 +11372,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t> 434,54 € </a:t>
+            <a:t> 434,49 € </a:t>
           </a:fld>
           <a:endParaRPr lang="de-DE" sz="2800" b="1">
             <a:ln>
@@ -11384,7 +11462,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t> 29,54 € </a:t>
+            <a:t> 29,51 € </a:t>
           </a:fld>
           <a:endParaRPr lang="de-DE" sz="2800" b="1">
             <a:ln>
@@ -12594,7 +12672,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t> 434,54 € </a:t>
+            <a:t> 434,49 € </a:t>
           </a:fld>
           <a:endParaRPr lang="de-DE" sz="2800" b="1">
             <a:ln>
@@ -12614,7 +12692,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Talla Fotsing Roméo" refreshedDate="46292.635019675923" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="62" xr:uid="{AECC3722-4F33-446B-9A76-E2824C46E9CC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Talla Fotsing Roméo" refreshedDate="46292.64685740741" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="62" xr:uid="{AECC3722-4F33-446B-9A76-E2824C46E9CC}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:W1048576" sheet="Auswertung"/>
   </cacheSource>
@@ -12635,16 +12713,16 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Käufe Stück" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5600530000000004" maxValue="2.5600530000000004"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5597650000000005" maxValue="2.5597650000000005"/>
     </cacheField>
     <cacheField name="Verkäufe Stück" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Bestand" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5600530000000004" maxValue="2.5600530000000004"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5597650000000005" maxValue="2.5597650000000005"/>
     </cacheField>
     <cacheField name="Investiert €" numFmtId="164">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="400.21000000000004" maxValue="400.21000000000004"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="400.20000000000005" maxValue="400.20000000000005"/>
     </cacheField>
     <cacheField name="Verkauft €" numFmtId="164">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
@@ -12653,28 +12731,28 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="5"/>
     </cacheField>
     <cacheField name="Netto P&amp;L €" numFmtId="164">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-405.21000000000004" maxValue="-405.21000000000004"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-405.20000000000005" maxValue="-405.20000000000005"/>
     </cacheField>
     <cacheField name="Status" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Einstandskurs €" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="158.19999999999999" maxValue="158.19999999999999"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="158.21" maxValue="158.21"/>
     </cacheField>
     <cacheField name="Aktueller Kurs €" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="169.74" maxValue="169.74"/>
     </cacheField>
     <cacheField name="Aktuell nicht realisierte P&amp;L €" numFmtId="166">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="29.543011620000073" maxValue="29.543011620000073"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="29.514090450000026" maxValue="29.514090450000026"/>
     </cacheField>
     <cacheField name="Aktuelle Position €" numFmtId="164">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="434.54339622000009" maxValue="434.54339622000009"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="434.49451110000012" maxValue="434.49451110000012"/>
     </cacheField>
     <cacheField name="Aktuell Investiert €" numFmtId="164">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="405.00038460000002" maxValue="405.00038460000002"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="404.9804206500001" maxValue="404.9804206500001"/>
     </cacheField>
     <cacheField name="Aktuelle Rendite" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="7.2945638432364276E-2" maxValue="7.2945638432364276E-2"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="7.2877820618165778E-2" maxValue="7.2877820618165778E-2"/>
     </cacheField>
     <cacheField name="Realisierte P&amp;L Verkäufe €" numFmtId="164">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
@@ -12692,7 +12770,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Gesamte Rendite" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="7.3295010669398697E-2" maxValue="7.3295010669398697E-2"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="7.3199677911044661E-2" maxValue="7.3199677911044661E-2"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -12709,26 +12787,26 @@
     <x v="0"/>
     <x v="0"/>
     <s v="IE00BK5BQT80"/>
-    <n v="2.5600530000000004"/>
+    <n v="2.5597650000000005"/>
     <n v="0"/>
-    <n v="2.5600530000000004"/>
-    <n v="400.21000000000004"/>
+    <n v="2.5597650000000005"/>
+    <n v="400.20000000000005"/>
     <n v="0"/>
     <n v="5"/>
-    <n v="-405.21000000000004"/>
+    <n v="-405.20000000000005"/>
     <s v="OFFEN"/>
-    <n v="158.19999999999999"/>
+    <n v="158.21"/>
     <n v="169.74"/>
-    <n v="29.543011620000073"/>
-    <n v="434.54339622000009"/>
-    <n v="405.00038460000002"/>
-    <n v="7.2945638432364276E-2"/>
+    <n v="29.514090450000026"/>
+    <n v="434.49451110000012"/>
+    <n v="404.9804206500001"/>
+    <n v="7.2877820618165778E-2"/>
     <n v="0"/>
     <n v="0"/>
     <n v="5"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="7.3295010669398697E-2"/>
+    <n v="7.3199677911044661E-2"/>
   </r>
   <r>
     <x v="1"/>
@@ -14259,7 +14337,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A3F31EA-6894-49F2-AD85-69A514AE323F}" name="PivotTable1" cacheId="224" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A3F31EA-6894-49F2-AD85-69A514AE323F}" name="PivotTable1" cacheId="234" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
   <location ref="L3:L4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
@@ -14302,7 +14380,7 @@
     <dataField name="Verkaufserlöse Gewinn/Verlust" fld="17" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="7">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14319,7 +14397,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E326F01-EA15-4A93-82D4-848E4D2615C7}" name="PivotTable9" cacheId="224" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E326F01-EA15-4A93-82D4-848E4D2615C7}" name="PivotTable9" cacheId="234" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
   <location ref="J3:J4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
@@ -14356,7 +14434,7 @@
     <dataField name="Einkaufswert" fld="15" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="8">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14373,7 +14451,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4A41211-FADE-4A81-A35B-B4ED20E62223}" name="PivotTable10" cacheId="224" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Assets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4A41211-FADE-4A81-A35B-B4ED20E62223}" name="PivotTable10" cacheId="234" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Assets">
   <location ref="E13:F16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0">
@@ -14433,7 +14511,7 @@
     <dataField name="Aktueller Wert" fld="14" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="9">
+    <format dxfId="35">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14485,7 +14563,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{223E5646-EA4E-4DBC-8347-0CFCE76D5F19}" name="PivotTable5" cacheId="224" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Assets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{223E5646-EA4E-4DBC-8347-0CFCE76D5F19}" name="PivotTable5" cacheId="234" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Assets">
   <location ref="A3:C6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0">
@@ -14554,7 +14632,7 @@
     <dataField name="Aktueller Wert" fld="14" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="10">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14591,7 +14669,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0769888-D3D4-498F-9981-49DFC80F5D0F}" name="PivotTable8" cacheId="224" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0769888-D3D4-498F-9981-49DFC80F5D0F}" name="PivotTable8" cacheId="234" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
   <location ref="G3:G4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
@@ -14628,7 +14706,7 @@
     <dataField name="Aktueller Wert" fld="14" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="11">
+    <format dxfId="37">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14645,7 +14723,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D646C2F3-32F0-4399-B83F-C10E1649A49F}" name="PivotTable6" cacheId="224" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" preserveFormatting="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" rowHeaderCaption="Assets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D646C2F3-32F0-4399-B83F-C10E1649A49F}" name="PivotTable6" cacheId="234" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" preserveFormatting="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" rowHeaderCaption="Assets">
   <location ref="A13:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField axis="axisRow" showAll="0">
@@ -14785,7 +14863,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9691FC7-B584-44C9-8056-E4ED1D6024DD}" name="PivotTable11" cacheId="224" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9691FC7-B584-44C9-8056-E4ED1D6024DD}" name="PivotTable11" cacheId="234" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
   <location ref="E3:E4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
@@ -14828,7 +14906,7 @@
     <dataField name="Aktueller Wert" fld="14" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="12">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14845,7 +14923,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{745C1A6C-3C9D-40E8-BB3C-38468AC3798B}" name="PivotTable12" cacheId="224" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{745C1A6C-3C9D-40E8-BB3C-38468AC3798B}" name="PivotTable12" cacheId="234" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Assets">
   <location ref="A8:D17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField axis="axisRow" subtotalTop="0" showAll="0" insertBlankRow="1">
@@ -14937,10 +15015,10 @@
     <dataField name="Aktueller Wert" fld="14" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="19">
+    <format dxfId="45">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="44">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14949,7 +15027,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -14958,7 +15036,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="42">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14967,7 +15045,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -14976,7 +15054,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14985,7 +15063,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -17683,29 +17761,29 @@
     <sortCondition ref="A2:A86"/>
   </sortState>
   <conditionalFormatting sqref="N2:N1048576">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:R1048576">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:W1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19444,19 +19522,19 @@
         <v>28</v>
       </c>
       <c r="B4" s="36">
-        <v>405.00038460000002</v>
+        <v>404.9804206500001</v>
       </c>
       <c r="C4" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
       <c r="E4" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
       <c r="G4" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
       <c r="J4" s="36">
-        <v>405.00038460000002</v>
+        <v>404.9804206500001</v>
       </c>
       <c r="L4" s="36">
         <v>0</v>
@@ -19477,27 +19555,27 @@
         <v>194</v>
       </c>
       <c r="B6" s="36">
-        <v>405.00038460000002</v>
+        <v>404.9804206500001</v>
       </c>
       <c r="C6" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
       <c r="E6" s="37">
         <f>GETPIVOTDATA("Aktuelle Position €",$E$3)</f>
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
       <c r="G6" s="37">
         <f>GETPIVOTDATA("Aktuelle Position €",$G$3)</f>
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
       <c r="H6" s="37"/>
       <c r="I6" s="37">
         <f>G6-J6</f>
-        <v>29.543011620000073</v>
+        <v>29.514090450000026</v>
       </c>
       <c r="J6" s="37">
         <f>GETPIVOTDATA("Aktuell Investiert €",$J$3)</f>
-        <v>405.00038460000002</v>
+        <v>404.9804206500001</v>
       </c>
       <c r="L6" s="37">
         <f>GETPIVOTDATA("Realisierte P&amp;L Verkäufe €",$L$3)</f>
@@ -19523,13 +19601,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F14" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -19537,7 +19615,7 @@
         <v>206</v>
       </c>
       <c r="B15" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>216</v>
@@ -19553,7 +19631,7 @@
         <v>194</v>
       </c>
       <c r="F16" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -19567,7 +19645,7 @@
         <v>194</v>
       </c>
       <c r="B18" s="36">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
     </row>
   </sheetData>
@@ -19613,13 +19691,13 @@
         <v>206</v>
       </c>
       <c r="B10" s="28">
-        <v>2.5600530000000004</v>
+        <v>2.5597650000000005</v>
       </c>
       <c r="C10" s="38">
         <v>169.74</v>
       </c>
       <c r="D10" s="38">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -19627,13 +19705,13 @@
         <v>200</v>
       </c>
       <c r="B11" s="28">
-        <v>2.5600530000000004</v>
+        <v>2.5597650000000005</v>
       </c>
       <c r="C11" s="38">
         <v>169.74</v>
       </c>
       <c r="D11" s="38">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -19677,13 +19755,13 @@
         <v>194</v>
       </c>
       <c r="B17" s="28">
-        <v>2.5600530000000004</v>
+        <v>2.5597650000000005</v>
       </c>
       <c r="C17" s="38">
         <v>169.74</v>
       </c>
       <c r="D17" s="38">
-        <v>434.54339622000009</v>
+        <v>434.49451110000012</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
